--- a/复制演示--源文件.xlsx
+++ b/复制演示--源文件.xlsx
@@ -4,10 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22192" windowHeight="10455"/>
+    <workbookView windowWidth="22192" windowHeight="10455" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="源数据" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="20">
   <si>
     <t>花名册</t>
   </si>
@@ -78,6 +80,15 @@
   </si>
   <si>
     <t>深圳</t>
+  </si>
+  <si>
+    <t>性别</t>
+  </si>
+  <si>
+    <t>出生年月</t>
+  </si>
+  <si>
+    <t>民族</t>
   </si>
 </sst>
 </file>
@@ -1151,4 +1162,237 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2">
+        <v>46145</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>1001</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2">
+        <v>45981</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>1002</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2">
+        <v>46037</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5">
+        <v>1003</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45512</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>1004</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="7"/>
+  <cols>
+    <col min="5" max="5" width="20.6548672566372"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2">
+        <v>46145</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3">
+        <v>1001</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45981</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>1002</v>
+      </c>
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46037</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5">
+        <v>1003</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45512</v>
+      </c>
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>1004</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>